--- a/Project_CNN/Main/Results/Experimento 7 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 7 - ResNet/training_metrics.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Main_Project\ResNet\Results\Experimento 7 - ResNet (500ep)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 7 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D67C11B-096C-48AD-89EF-364CCFCBCE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E226E0-C108-4E35-B507-CCA5D8AFC528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>epoch</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>val_loss</t>
+  </si>
+  <si>
+    <t>Variation</t>
+  </si>
+  <si>
+    <t>ResNet-18</t>
   </si>
 </sst>
 </file>
@@ -7147,6 +7153,6473 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>ResNet-18,</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> Batch Size = 32</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Worksheet!$B$2:$B$505</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="504"/>
+                <c:pt idx="0">
+                  <c:v>0.4481575191021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45236369967460999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45897483825683999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48288354277611001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50027167797089001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.51439958810805997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52898025512695002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.52870857715607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.53287446498871005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57788443565368997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.59219342470169001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.60025358200072998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.61166453361510997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.61945301294327004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.63267523050308005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.63140738010405995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.65178412199019997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.65368592739105003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.66382902860641002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.66681760549544999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.67270421981812001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.68293786048889005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.69407713413239003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.70702773332596003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.70014488697052002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.71291434764862005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.72495925426482999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.73147982358931996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.73283827304839999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.72631770372391002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.76046007871627996</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.77241444587707997</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.78273862600327004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.77667087316512995</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.77585583925247004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.78138017654419001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.79306286573410001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.78618001937866</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.78599894046783003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.79433071613312001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.79170441627501997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.79768157005310003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.79116100072860995</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.79568916559219005</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.79514580965042003</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.80094188451767001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.80067014694214</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.80601340532303001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.80338704586028997</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.80266255140304998</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.80782467126846003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.81334900856018</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.81072270870208996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.81307733058928999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.81099438667296997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.81190001964569003</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.81479805707931996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.81171888113021995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.80873030424117998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.81769609451294001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.82403552532196001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.82448834180831998</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82648068666457997</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.82376378774643</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.82675242424010997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.82693350315094005</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.82946932315826005</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.82566565275192005</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.82421660423278997</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.82430720329285001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.82738631963730003</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.82747691869735995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.82439774274826005</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.82910704612732</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.82965040206909002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.83010321855545</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.82575619220733998</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.82512223720551003</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.83073717355728005</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.82756745815277</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.83173340559006004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.83046549558640004</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.83001267910003995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.83182394504546997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.83263903856277</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.83109945058822998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.83354467153548994</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.83191448450089001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.83028435707091996</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.83336353302001998</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.83354467153548994</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.83535593748092996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.83363521099090998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.83263903856277</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.83544647693634</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.83327293395996005</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.83562761545180997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.83707660436630005</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.83300125598907004</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.83861619234085005</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.83689546585082997</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.83245790004730003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.83535593748092996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.83680492639542003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.83408802747725996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.84187644720078003</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.83780109882355003</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.83209562301635998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.83952182531357</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.83743888139724998</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.84287267923355003</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.83589929342269997</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.83617097139358998</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.83734828233719005</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.83879733085632002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.83852565288544001</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.83825391530991</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.83689546585082997</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.84006518125534002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.83680492639542003</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.83617097139358998</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.84223872423171997</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.83499366044998002</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.84151422977447998</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.84332549571991</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.84106141328812001</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.84241986274719005</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.83671438694</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.84042745828628995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.84151422977447998</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.83743888139724998</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.84368771314621005</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.84024631977080999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.84060859680176003</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.84341603517532004</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.84142363071441995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.84251040220260998</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.84269154071807995</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.83925014734268</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.84124255180358998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.84414052963257002</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.84296321868895996</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.84477448463439997</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.84640461206436002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.84622353315353005</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.83979350328445002</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.84341603517532004</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.84776306152344005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.84504616260528997</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.84884983301162997</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.84930264949798995</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.84404999017714999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.84685742855071999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.84486508369446001</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.84513676166534002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.84531790018081998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.85084223747252996</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.84586125612259</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.84993660449982</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.84740084409714</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.84703856706618996</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84097081422805997</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.85066109895705999</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.84830647706984996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.84966492652893</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.85047996044159002</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.85546094179152998</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85401195287704001</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.85591375827788996</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.85863065719604004</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.85075169801712003</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.85709112882614003</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.85374027490616</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.85174787044525002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.84622353315353005</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.85500812530518</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.85464590787887995</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.85745334625243996</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.85011774301528997</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.85618549585341996</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.8524723649025</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.85482704639435003</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.85663831233978005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.85120451450348</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.85600435733794999</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85645717382430997</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85835897922516002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.85229122638702004</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.85518926382064997</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.84839701652527</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.85364967584609996</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85582321882248003</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.85401195287704001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.85419309139251998</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.85980802774428999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.85971742868422996</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.85727220773696999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86180037260055997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.85419309139251998</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.85926461219787997</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.8613475561142</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.85808730125427002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.85618549585341996</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.86180037260055997</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.85953629016875999</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86243432760239003</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.86442673206329002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.85310631990432995</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.86343055963516002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.86071366071701005</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.86170983314514005</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.85953629016875999</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.85998910665511996</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.86723417043686002</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.85627603530884</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.86297774314880005</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.86107587814330999</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.86170983314514005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.85654771327972001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.86306828260421997</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.86515122652054</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.86542290449142001</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.86017024517059004</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.86587572097777998</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.86189097166061002</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.86152869462966997</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.86768698692321999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.86497008800507003</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.86632853746413996</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.86850208044052002</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.86324942111969005</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.86632853746413996</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.86660027503966996</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.86107587814330999</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.86524182558060003</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.86379277706145996</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.86487954854964999</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.87013220787047996</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.86388337612152</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.86442673206329002</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.86460787057876998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.86986052989960005</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.87303024530411</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.86813980340957997</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.86587572097777998</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.86759644746779996</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.86859261989594005</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.87583768367767001</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.86995106935500999</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.87022280693053999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.87022280693053999</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.86958885192871005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87085670232773005</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.86288714408875</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.86605685949325995</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.86759644746779996</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.87130951881409002</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.86660027503966996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.87284910678864003</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.86524182558060003</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.86995106935500999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.87284910678864003</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.86958885192871005</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.87076616287231001</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.87402641773223999</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.87004166841507002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.87230575084686002</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.86940771341323997</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.86913603544234996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.87303024530411</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87221515178679998</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.87312078475952004</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.87094730138778997</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.87357360124588002</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.87574714422225997</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.87511318922043002</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.87447923421859997</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.87520378828048995</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.87293970584868996</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.86850208044052002</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.87221515178679998</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.87049448490143</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.87565660476685003</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.87563222646713001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.87801122665404996</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.87665277719498003</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.87946021556854004</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.87112843990326005</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.87638109922409002</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.87810176610946999</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.87393587827681996</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.87493205070496005</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.87447923421859997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.87882632017135998</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.88290166854857999</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.88000363111496005</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.87185293436050004</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.87783008813857999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.87475097179412997</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.87728673219680997</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.87466037273407005</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.87936967611312999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.87275856733321999</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.87737727165222001</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.87728673219680997</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.88000363111496005</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.87737727165222001</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.88109040260314997</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.87955081462859996</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.87710559368134</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.88054698705672996</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.87918853759766002</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.87900739908217995</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.88217711448669001</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.88244885206223</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.88398838043213002</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.88145262002945002</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.88118094205856001</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.87955081462859996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.88389784097671997</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.88851654529571999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.88118094205856001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.88127148151398005</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.88978445529937999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.88317334651946999</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.88688641786574995</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.88362616300582997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.88480347394943004</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.88208657503127996</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.88453179597855003</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.88842600584029996</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.88471293449402</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.88435065746306996</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.88444119691848999</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.88661473989487005</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.88498461246490001</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.88516575098037997</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.88462233543395996</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.88697701692580999</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.88924109935759998</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.88326388597488004</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.88670527935027998</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.88951277732848999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.88806372880936002</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.88715809583663996</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.88389784097671997</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.89078062772750999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.88860714435577004</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.88733923435211004</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.88344502449036</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.89014673233032005</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.88869768381118996</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.89186739921570002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.88561856746673995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.89059954881668002</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.88833546638489003</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.88752037286758001</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.88489401340484997</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.88779205083847001</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.89132404327393</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.88770151138305997</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.89105236530303999</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.89132404327393</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.89213907718658003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.88905996084213001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.88915050029755005</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.89295417070389005</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.89286363124847001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.88987499475479004</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.88779205083847001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.89096176624297996</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.88824486732482999</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.88806372880936002</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.89087122678757003</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.89331644773482999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.89195799827575994</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.89621442556381004</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.89585220813750999</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.89096176624297996</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.89512771368027</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.89367866516113004</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.89213907718658003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.89376926422118996</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.89295417070389005</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.89331644773482999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.89259189367294001</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.89268249273300004</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.89693897962570002</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.89693897962570002</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.89041841030121005</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.89684838056563998</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.89639556407928001</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.89349752664565996</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.89087122678757003</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.89784461259841997</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.89530879259108997</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.89576160907744995</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.89938414096831998</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.89793515205383001</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.89476543664931996</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.89621442556381004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.89404094219207997</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.89150518178939997</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.89503711462020996</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.89358812570571999</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.89404094219207997</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.89349752664565996</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.89748233556747004</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.89539939165115001</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.89558053016662997</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.90038037300109997</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.89666724205017001</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.89548993110657005</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.89766347408295</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.89838796854018999</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>0.89566503365834615</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E666-4DB5-B7A9-04D7406FC248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Worksheet!$C$2:$C$505</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="504"/>
+                <c:pt idx="0">
+                  <c:v>1.4406977891921999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4298284053802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4208290576935001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4062652587891</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3887505531311</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3684068918228001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3479437828064</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3354363441467001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.3151044845580999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2629052400589</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2341845035553001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2075411081314</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1803368330002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1530569791794001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1298087835312001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1309546232223999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0854578018187999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0662350654602</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.0504486560821999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0443748235703001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.0266871452332</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.0102450847626001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.98921942710875999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.96063882112502996</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.95341974496840998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.92751413583755005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.92430961132050005</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.89992976188660001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.89259606599807995</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.90361022949219005</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.83080053329467995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.80003082752228005</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.78789383172989003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.78710055351257002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.78690278530121005</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.78032851219177002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.76915705204009999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.76983034610748002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.76991474628447998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.76210451126098999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.76324504613875999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.75206923484802002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.76296037435532005</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.75216430425643999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.75532370805740001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.74256753921509</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.73892277479171997</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.73824298381804998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.74144601821899003</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.73381584882735995</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.72748094797134</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.72514432668686002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72582536935805997</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.71874892711639005</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.72013884782791004</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.71924841403961004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.71712577342987005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.71662992238998002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.72472494840622004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.70936220884322998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.69820392131804998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.68987339735030995</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.68802946805954002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.69250911474228005</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.69081181287766003</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.69147115945815996</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.68581539392471003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.68021816015243997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68375444412231001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.68681472539902</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.68708336353302002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.68218737840652</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.69401586055756004</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.69173425436019997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.67598456144332997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.67763650417328003</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.67841529846190995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.67467319965363004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.68387293815613004</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.68034273386001998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.68033671379089</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.68260955810546997</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.67443764209747004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.67914330959320002</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.67708629369735995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.67256402969359996</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.67768996953964</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.67586934566498003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.67533004283904996</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.67051649093627996</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.67692214250564997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.68183654546738004</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.67157560586928999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.67005044221877996</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.67227947711945002</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.67463409900664995</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.66906577348708995</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.66290527582169001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.67526853084563998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.67312425374984997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.66384434700011996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.66846781969070002</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.67119771242142001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.66236078739166004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.66920840740204002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.66769844293594005</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.66950136423110995</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.66684406995773005</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.66741394996643</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.66634470224380005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.66678345203400002</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.66316658258437999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.66188192367554</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.66320151090622004</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.65727442502974998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.67609947919846003</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.66167116165161</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.66182345151901001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.66000795364380005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.66879117488860995</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.66523331403732</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.66352319717407005</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.66349363327026001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.66560417413712003</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.66024339199065996</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.65825492143631004</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.66037970781326005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.66175103187561002</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.66021662950516002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.66000962257384999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.66417700052260997</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.65122139453887995</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.65798401832580999</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.65598350763321001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.65451425313949996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.66527813673018998</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.65370351076125999</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.65338259935378995</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.65456831455231002</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.65266078710555997</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.66042584180831998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.65117979049682995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.65773677825928001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.65804326534270996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.64781945943831998</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.65182799100875999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.65531468391418002</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.65116077661514005</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.65085798501967995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.64598214626312001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.65009653568268</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.65241485834122004</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.65296119451523005</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.64257222414017001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.65040284395217995</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.65050595998764005</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.65029805898666004</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.65243500471115001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.64848917722702004</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.65267115831375</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.64629203081131004</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.64366763830185003</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.64368426799774003</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.65140151977538996</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.64762634038925004</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.64197736978530995</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.64283907413482999</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.65015321969985995</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.63833272457123003</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.64979982376098999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.64361178874969005</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.64200788736342995</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.64274299144744995</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.64151966571807995</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.63740879297256003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.64138352870940996</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.64177381992339999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.64226359128952004</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.64727646112442005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.63579326868056996</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.64399790763855003</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.63754063844680997</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.63304144144058005</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.64059734344482</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.63862478733062999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.64382725954055997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.63444602489471003</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.63770157098769997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.63864731788634999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.63362580537795998</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.63648098707198997</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.64417660236358998</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.63457399606705001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.63827055692672996</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.63403081893920998</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.63915997743607</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.62996327877045</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.63424587249756004</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.63526856899260997</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.62732636928558005</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.62880814075470004</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.63018906116485995</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.62871754169464</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.63364851474761996</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.63177222013473999</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.63151830434798994</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.63606822490692005</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.62795424461365001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.62465864419937001</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.63500785827636996</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.63246124982833996</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.62248766422271995</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.62471240758895996</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.62781780958176003</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.63424676656723</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.62509107589722002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.62984251976012995</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.6232550740242</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.62869107723235995</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.625643491745</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.62965095043181996</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.62040036916732999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.62495261430740001</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.62477827072143999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.62174147367476995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.62538033723830999</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.62155485153197998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.61980527639389005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.62362462282180997</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.61650705337524003</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.61714786291122004</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.62161386013030995</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.62581014633179</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.61496883630752996</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.63054633140563998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.62374836206436002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.62215042114258001</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.62357413768768</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.62226361036301003</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.61762791872025002</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.61369776725768999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.61406075954437001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.62237358093261996</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.61404317617416004</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.61214011907578003</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.60362744331359997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.6160860657692</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.61678147315979004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.61115884780884</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.62058061361312999</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.61470067501068004</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.61079758405685003</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.62178897857666005</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.61141848564148005</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.60553473234177002</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.61033362150192005</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.60685878992080999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.61136513948440996</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.60736632347107</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.60223168134688998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.60869270563125999</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.61384242773055997</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.60882234573364002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.61038088798523005</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.60640394687652999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.60980784893036</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.61263281106948997</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.60337948799133001</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.61346220970153997</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.60192245244980003</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.60510683059692005</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.60907703638077004</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.60989814996719005</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.60349583625793002</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.60650140047072998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.60594260692596003</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.61063706874847001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.60467219352722001</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.61172050237655995</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.59723961353302002</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.60951405763625999</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.60568690299988004</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.60417318344116</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.60714185237884999</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.60602873563766002</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.60009092092514005</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.59863734245300004</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.59709835052490001</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.59729039669036998</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.59869396686553999</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.60557097196579002</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.59698647260666005</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.60148632526398005</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.59903532266616999</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.59185552597045998</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.59384787082671997</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.59743016958237005</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.60152554512024003</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.59993463754653997</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.60144066810607999</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.59439849853516002</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.58889120817184004</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.59083771705626997</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.59273105859756003</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.59599107503891002</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.59030747413634999</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.58774048089981001</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.58280164003372004</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.59304714202881004</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.5954784154892</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.58754396438598999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.59086012840270996</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.59462344646454002</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.59390819072723</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.59825044870376998</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.59080630540848</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.59377431869507002</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.58437627553939997</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.59742039442062</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.58782732486724998</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.59141027927399004</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.58784109354018999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.58761453628539995</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.58488672971724998</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.58704209327697998</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.59094166755676003</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.58067506551742998</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.58555406332016002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.58505105972289995</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.58690524101257002</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.58450716733931996</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.58629256486893</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.57920229434966997</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.58189457654953003</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.58312696218491</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.58162289857864002</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.5861234664917</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.57904785871506004</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.58337271213530995</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.57686352729796997</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.57948267459868996</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.58045768737793002</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.58118981122971003</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.58691185712813998</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.58582657575607</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.58433008193970004</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.57133096456527999</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.57925266027450995</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.57413274049759</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.57557421922684004</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.57631897926330999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.58366733789444003</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.57956224679946999</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.57674151659011996</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.57845199108124001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.57828855514526001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.57975417375564997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.57249563932419001</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.57214885950089001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.57411843538284002</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.57696282863616999</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.57227218151092996</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.58040148019791005</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.57468616962432995</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.58143436908722002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.56927800178527999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.57960104942321999</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.57312339544295998</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.57618528604507002</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.57663750648499001</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.57285660505295</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.56652373075484996</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.57141607999802002</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.56885623931884999</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.56605666875839</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.57275027036667003</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.56716805696487005</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.56556379795073997</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.56860691308974998</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.56665545701981002</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.55756270885467996</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.56325238943099998</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.56794607639312999</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.56882566213607999</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.56647771596909002</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.56903928518294999</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.55689394474029996</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.56617408990859996</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.56762802600860995</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.56244212388991999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.56097650527954002</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.56447285413741999</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.55367952585220004</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.56133174896240001</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.56240791082382002</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.56094205379485995</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.56044572591782005</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.56646698713303001</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.55825304985045998</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.55903464555740001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.56410199403762995</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.56106901168822998</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.56194603443145996</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.56225794553757003</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.55817490816116</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.55940824747086004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.55307239294052002</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.55575817823410001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.55783081054688</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.55579960346222002</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.55684894323348999</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.56020772457123003</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.55834895372391002</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.55186831951141002</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.55347383022308005</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.55319404602051003</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.56091678142547996</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.55814170837402</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.55090177059173995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.54941534996033004</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.55794274806975996</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.55236214399338002</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.55097073316573997</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.55610853433608998</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.55156975984572998</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.55075782537460005</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.55138504505157004</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.54642039537429998</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.55230522155761996</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.54856395721436002</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.55178344249724998</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.54594129323958995</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.55098861455917003</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.54590451717376998</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.55110985040664995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.54773342609405995</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.55010902881622004</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.54891049861908003</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.55430179834366</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.54408347606659002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.54301697015761996</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.55048954486847002</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.54474425315857</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.54606527090072998</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.54355281591414994</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.54741942882537997</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.54531270265579002</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.53970211744308005</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.54389065504073997</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.54389286041259999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.54813659191132003</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.54029923677444003</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.54132914543152</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.54399508237839</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.54859685897827004</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.54602015018463002</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.54392653703689997</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.53627169132232999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.54210621118545999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.53788053989410001</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.53622096776962003</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.54354208707809004</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.53701698780060003</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.53618252277374001</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.53442192077636996</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.53679859638214</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.53910958766937001</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.53943747282027998</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.53262323141098</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.53464889526366999</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.54381310939788996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.53711748123169001</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.52948796749115001</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.54336220026016002</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.53102648258208995</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.53091269731521995</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.53247523307800004</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.53513622283936002</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.53836148977279996</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.52965354919434005</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.52863311767578003</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.53231972455978005</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.52467608451842995</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.52876657247543002</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.52638524770737005</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.53357666730881004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.53293949365616</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.53173786401749001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.53014487028122004</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.53341072797775002</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.53427726030349998</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.53062808513641002</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.53003776073455999</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.53200578689574995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.52994835376740002</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.51979041099547996</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.53003072738646995</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.52739816904068004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.53156578540802002</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.52679747343062999</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>0.53028596242268866</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E666-4DB5-B7A9-04D7406FC248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Worksheet!$E$2:$E$505</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="504"/>
+                <c:pt idx="0">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.48037791252135997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55632269382476995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.55123543739319003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.52943313121795998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54796510934830001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.57885175943375</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.61046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.59738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63880813121795998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.63662791252135997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64643895626068004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.59375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67914241552353005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.70094478130340998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.66787791252135997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.70784884691238004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.71039241552353005</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67260175943375</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.72892439365386996</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.69476741552353005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.75109010934830001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.73473834991455</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.74781978130340998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.77434593439101995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.78706395626068004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.75617730617523005</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.77434593439101995</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.77761626243590998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.796875</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.79978197813034002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.80377906560898005</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.81431686878204002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.81468021869659002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.81577032804489003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.81867730617523005</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.82267439365386996</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.82449126243590998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.82122093439101995</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.81758719682693004</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.88517439365386996</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.88590115308761996</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.890625</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.88844478130340998</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.88735467195510997</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>0.58604896068572998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E666-4DB5-B7A9-04D7406FC248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Worksheet!$F$2:$F$505</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="504"/>
+                <c:pt idx="0">
+                  <c:v>1.4361934661864999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4307509660721001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4052577018737999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3754277229309</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3661518096923999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3501120805739999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3004044294357</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2764148712158001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2630277872086</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2126594781875999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1598023176193</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1371423006057999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1160435676575</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1636548042296999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.045276761055</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.99371296167374001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0278086662292001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.98931795358658003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.94671553373337003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0286920070648</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.940185546875</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.98723405599594005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.88305371999741</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.91053789854050005</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.88849622011185003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.85853648185730003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.80953085422516002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.84911733865738004</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.81871610879898005</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.82156008481979004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.76237583160400002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.74671339988707996</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.77687740325928001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.74736100435257002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.74868392944336004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.72836571931839</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.73106151819229004</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.72806704044341997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.73575246334076005</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.72907245159149003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.72422081232071001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.71847593784331998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.71365159749984997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.71058726310730003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.70509552955626997</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.70530325174331998</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.70703458786010998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.70862483978270996</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.70495098829268998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.72236871719359996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.72097665071487005</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.68901306390761996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.70739382505417003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.68891012668609997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.69268333911895996</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.68901318311690996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.67847937345505005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.68004256486893</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.67718452215195002</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.68661648035049005</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.66792684793472001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.66277772188187001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.66541266441345004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.66182440519332997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.66285985708237005</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.66303002834320002</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66351169347762995</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.66292148828506003</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.66474473476410001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.66265285015106001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.66209328174590998</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.66709977388382002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.66018623113632002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.66674137115479004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.66237974166869995</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.66118007898330999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.66257828474045</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.66542327404021995</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.66148191690445002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.66036611795425004</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.66117841005324995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.66140288114547996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.66057592630385997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.65853059291839999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.65999358892440996</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.66188651323318004</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.65792250633240001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.65890890359878995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.66175365447998002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.65896499156952004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.66266483068465998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.65893411636353005</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.65703976154327004</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.65795350074768</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.65979021787643</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.66289514303206998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.65925794839858998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.66066980361937999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.65910798311233998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.65752142667769997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.66536480188369995</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.66389930248259998</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.66129571199417003</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.66523420810698997</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.66035556793213002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.65967059135437001</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.65660750865936002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.65593016147614003</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.65442943572998002</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.65566879510880005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.65707021951675004</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.65316504240036</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.66011482477187999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.65230160951614002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.65362584590911998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.65058881044387995</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.65569585561751997</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.65105187892913996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.65730214118957997</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.65272849798203003</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.65191924571991</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.65411281585693004</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.65230619907378995</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.65147632360457997</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.64930856227875</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.65302526950836004</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.65301209688187001</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.65405458211899004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.65601843595505005</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.65109848976134999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.65261822938919001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.65386015176773005</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.65719109773635997</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.65102839469910001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.65074127912520996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.64682948589324996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.64929026365279996</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.65405982732773005</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.64795023202895996</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.64897894859313998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.65351706743240001</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.64676517248153997</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.65270948410034002</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.64852166175841996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.64923554658890004</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.64678204059600997</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.64842140674590998</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.64653384685516002</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.65552234649658003</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.65187388658524004</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.64557898044586004</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.64601957798003995</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.65502142906188998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.65161454677581998</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.64921116828918002</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.64012098312377996</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.64829117059707997</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.64436423778534002</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.65105843544006003</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.65071147680283004</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.64943343400955</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.64528810977936002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.64476436376571999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.64066499471663996</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.64791440963744995</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.64545118808746005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.65082627534866</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.63826495409011996</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.63924223184586004</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.63564795255661</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.64335000514983998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.63993620872498003</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.64919883012771995</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.65243417024612005</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.64155817031859996</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.6458158493042</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.64306831359863004</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.63922154903411998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.65426355600357</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.64206492900848</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.64274334907532005</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.63450926542282005</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.64134812355042004</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.64199888706206998</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.63859307765961004</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.63307785987854004</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.64676868915557995</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.64108908176421997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.63432365655899003</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.64501684904098999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.63303607702255005</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.65184032917023005</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.64467781782150002</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.64287483692169001</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.63645887374877996</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.64468401670455999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.64038300514221003</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.63529145717621005</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.63284087181090998</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.64414280653</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.63833069801330999</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.63709586858749001</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.64945369958877996</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.63674116134643999</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.63963353633881004</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.63105607032776001</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.63966763019562001</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.63125163316726995</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.63474756479262995</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.63040822744369995</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.63240969181061002</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.63184380531311002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.63210546970366999</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.62853509187697998</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.63682943582535001</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.63018268346785999</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.62706339359283003</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.62762564420699996</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.63013684749603005</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.62570470571518</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.62745904922484996</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.63280564546585005</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.62563139200211004</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.63645488023758001</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.62563377618789995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.63472199440001997</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.63447284698485995</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.63061743974686002</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.63336658477783003</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.64411902427672996</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.63389110565186002</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.63759934902190996</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.63208329677581998</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.62914520502089999</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.63256752490997004</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.62937700748444003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.63697075843811002</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.62627696990966997</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.62222045660018999</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.62624162435532005</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.62974488735198997</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.63852208852768</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.62484544515609997</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.62388008832931996</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.62950974702835005</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.63307958841323997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.62823170423508001</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.63096541166305997</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.62229984998703003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.62744200229644997</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.63735830783844005</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.62575042247771995</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.62191456556320002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.62585502862929998</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.62310034036635997</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.62597191333770996</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.62109309434891002</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.62465822696686002</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.63010209798812999</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.62737405300140003</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.61740034818649003</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.62140136957169001</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.62461894750595004</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.61999863386153997</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.63139045238494995</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.61794149875641002</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.61867171525955</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.62353301048278997</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.62886297702788996</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.62240505218506004</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.61849862337112005</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.62328416109085005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.61974108219146995</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.63293367624283003</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.61912447214126998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.61586773395537997</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.61618518829346003</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.61314970254898005</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.61647635698318004</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.62526214122771995</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.61402493715286</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.61564338207244995</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.61154192686080999</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.61596858501434004</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.61183881759643999</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.62156075239181996</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.60795140266418002</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.62896084785461004</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.61324298381804998</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.61766350269318004</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.61175030469893998</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.61600619554519997</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.61047440767287997</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.62007993459702004</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.62216216325759999</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.61615008115768</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.62262463569641002</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.62283438444137995</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.61182826757430997</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.61115849018097002</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.61128115653991999</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.61785548925400002</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.61346459388732999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.60389560461044001</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.62417799234390003</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.61264348030089999</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.6250776052475</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.62394541501999001</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.61457169055938998</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.60925060510634999</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.62205410003661998</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.61142462491989003</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.60166394710541005</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.63674569129944003</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.62179523706436002</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.61560881137848</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.60988730192184004</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.60760110616684004</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.60008782148360995</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.61690568923949995</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.60260307788848999</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.62595617771149004</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.60492575168609997</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.60891038179398005</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.60414391756057995</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.61476355791091997</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.61356246471404996</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.62517988681793002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.60639345645904996</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.61394017934798994</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.63017266988753995</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.60859304666518999</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.60548090934752996</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.61299365758895996</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.60171061754226995</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.66663545370101995</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.67194026708603005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.61060231924056996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.60173338651657005</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.60817587375641002</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.60734343528748003</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.61804533004760998</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.59910911321640004</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.60789966583251998</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.60122996568679998</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.59656083583831998</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.60285353660582996</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.60145956277847001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.61086058616637995</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.61340099573134999</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.60503137111663996</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.60508275032043002</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.61127859354018999</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.61585837602615001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.61154156923294001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.59700286388396995</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.60763299465178999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.61689168214797996</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.59656029939651001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.60076278448105003</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.59530425071715998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.59724992513657005</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.59547591209411999</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.59990763664246005</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.59763425588607999</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.59245300292969005</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.59211146831511996</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.59349304437636996</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.59535980224608998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.59873503446579002</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.60545182228088001</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.60026210546493997</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.59566736221312999</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.59291344881057995</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.60548651218413996</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.59448510408401001</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.59620797634125</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.61984151601791004</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.59519273042679</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.59804517030715998</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.61276441812515003</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.59673959016800004</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.59653663635253995</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.60913974046706998</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.59312725067139005</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.60541784763336004</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.59530615806580001</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.59171861410141002</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.60065883398055997</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.60030704736710006</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.59092539548874001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.60393702983856001</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.60319906473160001</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.61200153827667003</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.59669774770737005</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.60536849498749001</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.61706495285034002</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.60610175132750999</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.61129295825957997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.59024178981780995</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.60544973611831998</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.59924131631850996</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.60055267810821999</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.60400575399399004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.58661222457885998</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.58562302589417004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.60190588235855003</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.59041762351990001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.58837240934372004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.60231596231461004</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.59107589721679998</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.59808027744293002</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.59140795469284002</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.59379458427428999</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.59425866603850996</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.60856026411056996</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.58861809968947998</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.60130608081818004</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.58786147832869995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.59691649675368996</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.58554255962372004</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.58953946828841997</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.59474676847457997</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.59888994693756004</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.58665198087692005</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.59278243780135997</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.59572386741637995</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.58991336822509999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.59166508913039995</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.59931957721710005</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.58525979518890003</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.59553438425063998</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.59644615650177002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.59883373975753995</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.59007048606873003</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.60907024145125999</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.59952729940413996</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.63677644729614002</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.60458850860596003</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.58986705541610995</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.59956026077270996</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.59056586027144997</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.60114771127701006</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.59629631042480002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.59349018335341996</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.58242964744568004</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.58812671899795999</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.59490752220153997</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.59070926904678001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.59605365991591996</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.58426707983017001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.58659875392913996</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.61475092172623003</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.60190719366073997</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.58706218004226995</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.58108228445053001</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.60289865732193004</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.59364825487136996</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.60121876001357999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.57755494117737005</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.59022361040115001</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.58361071348189997</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.61394006013869995</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.58312940597534002</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.59261262416839999</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.58893561363220004</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.59511393308640004</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.59788817167282005</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.59076535701751998</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.59031736850739003</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.58729511499404996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.60406601428985995</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.59386682510375999</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.58174538612366</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.59273743629455999</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.59412395954132002</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.59550172090529996</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.58716380596161</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.58415824174881004</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.58705812692642001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.58457297086715998</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.60028058290482</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.58216553926467995</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.57830303907393998</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.58640056848526001</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.58561581373214999</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.58254170417786</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.59765160083770996</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.59431689977645996</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.57976353168488004</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.58144265413284002</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.58583104610443004</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.59382694959641003</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.58641046285628995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.58390516042708995</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.58429884910582996</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.57986408472061002</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.59671485424042003</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.57700878381729004</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.58154201507568004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E666-4DB5-B7A9-04D7406FC248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="870452783"/>
+        <c:axId val="870453263"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="870452783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="870453263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="870453263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="870452783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7268,6 +13741,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9371,6 +15884,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -9399,7 +16428,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6344478" y="381000"/>
+          <a:off x="7040217" y="381000"/>
           <a:ext cx="4595192" cy="5505450"/>
           <a:chOff x="6324600" y="381000"/>
           <a:chExt cx="4572000" cy="5505450"/>
@@ -9453,13 +16482,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>308527</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>3727</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
@@ -9476,7 +16505,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10968245" y="381000"/>
+          <a:off x="11639136" y="381000"/>
           <a:ext cx="4598504" cy="5505450"/>
           <a:chOff x="6334125" y="6296025"/>
           <a:chExt cx="4572000" cy="5505450"/>
@@ -9525,6 +16554,42 @@
         </a:graphic>
       </xdr:graphicFrame>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>612912</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3313</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>612912</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Gráfico 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DBDBFF4-0861-8811-410B-DFED64DA836D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9817,11 +16882,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F501"/>
+  <dimension ref="A1:F505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
   </cols>
@@ -19846,6 +26913,44 @@
         <v>0.58154201507568004</v>
       </c>
     </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>7</v>
+      </c>
+      <c r="B505">
+        <f>AVERAGE(B487:B501)</f>
+        <v>0.89566503365834615</v>
+      </c>
+      <c r="C505">
+        <f>AVERAGE(C487:C501)</f>
+        <v>0.53028596242268866</v>
+      </c>
+      <c r="D505">
+        <f>AVERAGE(E487:E501)</f>
+        <v>0.88321221272150663</v>
+      </c>
+      <c r="E505">
+        <f>AVERAGE(F487:F501)</f>
+        <v>0.58604896068572998</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Project_CNN/Main/Results/Experimento 7 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 7 - ResNet/training_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 7 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E226E0-C108-4E35-B507-CCA5D8AFC528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4572EDD-F109-4339-A923-4B3DA8667957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13620,6 +13620,6989 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" baseline="0"/>
+              <a:t>Accuracy curve: ResNet-18, Batch size = 32</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1600" b="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$B$2:$B$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.4481575191021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45236369967460999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45897483825683999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48288354277611001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50027167797089001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.51439958810805997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52898025512695002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.52870857715607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.53287446498871005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57788443565368997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.59219342470169001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.60025358200072998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.61166453361510997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.61945301294327004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.63267523050308005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.63140738010405995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.65178412199019997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.65368592739105003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.66382902860641002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.66681760549544999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.67270421981812001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.68293786048889005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.69407713413239003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.70702773332596003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.70014488697052002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.71291434764862005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.72495925426482999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.73147982358931996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.73283827304839999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.72631770372391002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.76046007871627996</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.77241444587707997</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.78273862600327004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.77667087316512995</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.77585583925247004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.78138017654419001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.79306286573410001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.78618001937866</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.78599894046783003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.79433071613312001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.79170441627501997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.79768157005310003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.79116100072860995</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.79568916559219005</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.79514580965042003</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.80094188451767001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.80067014694214</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.80601340532303001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.80338704586028997</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.80266255140304998</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.80782467126846003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.81334900856018</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.81072270870208996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.81307733058928999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.81099438667296997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.81190001964569003</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.81479805707931996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.81171888113021995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.80873030424117998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.81769609451294001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.82403552532196001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.82448834180831998</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82648068666457997</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.82376378774643</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.82675242424010997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.82693350315094005</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.82946932315826005</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.82566565275192005</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.82421660423278997</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.82430720329285001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.82738631963730003</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.82747691869735995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.82439774274826005</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.82910704612732</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.82965040206909002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.83010321855545</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.82575619220733998</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.82512223720551003</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.83073717355728005</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.82756745815277</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.83173340559006004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.83046549558640004</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.83001267910003995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.83182394504546997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.83263903856277</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.83109945058822998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.83354467153548994</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.83191448450089001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.83028435707091996</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.83336353302001998</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.83354467153548994</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.83535593748092996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.83363521099090998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.83263903856277</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.83544647693634</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.83327293395996005</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.83562761545180997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.83707660436630005</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.83300125598907004</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.83861619234085005</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.83689546585082997</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.83245790004730003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.83535593748092996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.83680492639542003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.83408802747725996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.84187644720078003</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.83780109882355003</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.83209562301635998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.83952182531357</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.83743888139724998</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.84287267923355003</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.83589929342269997</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.83617097139358998</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.83734828233719005</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.83879733085632002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.83852565288544001</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.83825391530991</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.83689546585082997</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.84006518125534002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.83680492639542003</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.83617097139358998</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.84223872423171997</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.83499366044998002</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.84151422977447998</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.84332549571991</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.84106141328812001</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.84241986274719005</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.83671438694</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.84042745828628995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.84151422977447998</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.83743888139724998</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.84368771314621005</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.84024631977080999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.84060859680176003</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.84341603517532004</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.84142363071441995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.84251040220260998</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.84269154071807995</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.83925014734268</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.84124255180358998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.84414052963257002</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.84296321868895996</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.84477448463439997</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.84640461206436002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.84622353315353005</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.83979350328445002</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.84341603517532004</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.84776306152344005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.84504616260528997</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.84884983301162997</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.84930264949798995</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.84404999017714999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.84685742855071999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.84486508369446001</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.84513676166534002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.84531790018081998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.85084223747252996</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.84586125612259</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.84993660449982</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.84631407260894997</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.84740084409714</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.84703856706618996</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.84649521112442005</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84097081422805997</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.84568011760712003</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.85066109895705999</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.84830647706984996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.84966492652893</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.85047996044159002</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.85546094179152998</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85401195287704001</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.85591375827788996</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.85863065719604004</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.85075169801712003</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.85709112882614003</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.85374027490616</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.85174787044525002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.84622353315353005</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.85500812530518</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.85464590787887995</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.85745334625243996</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.85011774301528997</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.85618549585341996</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.8524723649025</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.85482704639435003</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.85663831233978005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.85120451450348</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.85600435733794999</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85645717382430997</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85835897922516002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.85229122638702004</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.85518926382064997</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.84839701652527</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.85364967584609996</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85582321882248003</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.85401195287704001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.85419309139251998</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.85980802774428999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.85971742868422996</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.85727220773696999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86180037260055997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.85636657476425004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.85419309139251998</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.85926461219787997</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.8613475561142</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.85808730125427002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.85618549585341996</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.86180037260055997</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.85953629016875999</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86243432760239003</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.86442673206329002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.85310631990432995</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.86343055963516002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.86071366071701005</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.86170983314514005</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.85953629016875999</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.85998910665511996</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.86723417043686002</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.85627603530884</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.86297774314880005</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.86107587814330999</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.86170983314514005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.85654771327972001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.86306828260421997</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.86515122652054</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.86542290449142001</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.86017024517059004</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.86587572097777998</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.86189097166061002</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.86152869462966997</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.86768698692321999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.86497008800507003</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.86632853746413996</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.86850208044052002</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.86324942111969005</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.86632853746413996</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.86660027503966996</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.86107587814330999</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.86524182558060003</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.86379277706145996</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.86487954854964999</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.87013220787047996</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.86388337612152</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.86442673206329002</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.86460787057876998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.86986052989960005</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.87303024530411</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.86813980340957997</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.86587572097777998</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.86759644746779996</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.86859261989594005</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.87583768367767001</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.86995106935500999</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.87022280693053999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.87022280693053999</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.86958885192871005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87085670232773005</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.86288714408875</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.86605685949325995</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.86759644746779996</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.87130951881409002</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.86660027503966996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.87284910678864003</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.86524182558060003</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.86995106935500999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.87284910678864003</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.86958885192871005</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.87076616287231001</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.87402641773223999</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.87004166841507002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.87230575084686002</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.86940771341323997</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.86913603544234996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.87303024530411</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87221515178679998</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.87312078475952004</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.87094730138778997</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.87357360124588002</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.87574714422225997</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.87511318922043002</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.87447923421859997</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.87520378828048995</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.87293970584868996</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.86850208044052002</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.87221515178679998</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.87049448490143</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.87565660476685003</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.87563222646713001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.87801122665404996</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.87665277719498003</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.87946021556854004</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.87112843990326005</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.87638109922409002</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.87810176610946999</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.87393587827681996</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.87493205070496005</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.87447923421859997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.87882632017135998</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.88290166854857999</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.88000363111496005</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.87185293436050004</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.87783008813857999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.87475097179412997</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.87728673219680997</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.87466037273407005</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.87936967611312999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.87275856733321999</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.87737727165222001</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.87728673219680997</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.88000363111496005</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.87737727165222001</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.88109040260314997</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.87955081462859996</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.87710559368134</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.88054698705672996</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.87918853759766002</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.87900739908217995</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.88217711448669001</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.88244885206223</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.88398838043213002</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.88145262002945002</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.88118094205856001</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.87955081462859996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.88389784097671997</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.88851654529571999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.88118094205856001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.88127148151398005</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.88978445529937999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.88317334651946999</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.88688641786574995</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.88362616300582997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.88480347394943004</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.88199603557587003</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.88208657503127996</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.88453179597855003</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.88842600584029996</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.88471293449402</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.88435065746306996</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.88090926408768</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.88444119691848999</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.88380730152130005</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.88661473989487005</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.88570910692214999</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.88498461246490001</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.88516575098037997</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.88462233543395996</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.88697701692580999</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.88924109935759998</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.88326388597488004</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.88670527935027998</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.88951277732848999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.88806372880936002</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.88715809583663996</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.88389784097671997</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.89078062772750999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.88860714435577004</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.88733923435211004</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.88344502449036</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.89014673233032005</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.88869768381118996</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.89186739921570002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.88561856746673995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.89059954881668002</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.88833546638489003</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.88752037286758001</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.88489401340484997</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.88779205083847001</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.89132404327393</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.88770151138305997</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.89105236530303999</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.89132404327393</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.89213907718658003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.88905996084213001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.88915050029755005</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.89295417070389005</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.89286363124847001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.88987499475479004</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.88779205083847001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.89096176624297996</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.88824486732482999</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.88806372880936002</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.89087122678757003</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.89331644773482999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.89195799827575994</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.89621442556381004</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.89585220813750999</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.89096176624297996</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.89512771368027</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.89367866516113004</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.89213907718658003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.89376926422118996</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.89295417070389005</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.89331644773482999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.89259189367294001</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.89268249273300004</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.89693897962570002</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.89693897962570002</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.89041841030121005</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.89684838056563998</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.89639556407928001</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.89349752664565996</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.89087122678757003</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.89784461259841997</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.89530879259108997</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.89576160907744995</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.89938414096831998</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.89793515205383001</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.89476543664931996</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.89621442556381004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.89404094219207997</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.89150518178939997</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.89503711462020996</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.89358812570571999</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.89404094219207997</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.89349752664565996</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.89748233556747004</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.89539939165115001</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.89558053016662997</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.90038037300109997</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.89666724205017001</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.89548993110657005</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.89766347408295</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.89838796854018999</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-792D-4D75-80D2-2D6D5D5CDFEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$E$2:$E$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.48037791252135997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55632269382476995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.55123543739319003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.52943313121795998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54796510934830001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.57885175943375</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.61046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.59738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63880813121795998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.63662791252135997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64643895626068004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.59375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67914241552353005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.70094478130340998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.66787791252135997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.70784884691238004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.71039241552353005</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67260175943375</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.72892439365386996</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.69476741552353005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.75109010934830001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.73473834991455</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.74781978130340998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.77434593439101995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.78706395626068004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.75617730617523005</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.77434593439101995</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.77761626243590998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.796875</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.79978197813034002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.80377906560898005</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.81431686878204002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.81468021869659002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.81577032804489003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.81867730617523005</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.82267439365386996</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.82449126243590998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.82122093439101995</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.81758719682693004</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.86991280317306996</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.88517439365386996</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.88590115308761996</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.890625</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.88844478130340998</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.88081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.88735467195510997</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-792D-4D75-80D2-2D6D5D5CDFEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="393590320"/>
+        <c:axId val="393592720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="393590320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393592720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="393592720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Accuracy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0"/>
+                  <a:t> (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1600" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393590320"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Loss curve: ResNet-18, Batch size = 32</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$C$2:$C$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.4406977891921999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4298284053802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4208290576935001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4062652587891</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3887505531311</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3684068918228001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3479437828064</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3354363441467001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.3151044845580999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2629052400589</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2341845035553001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2075411081314</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1803368330002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1530569791794001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1298087835312001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1309546232223999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0854578018187999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0662350654602</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.0504486560821999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0443748235703001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.0266871452332</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.0102450847626001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.98921942710875999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.96063882112502996</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.95341974496840998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.92751413583755005</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.92430961132050005</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.89992976188660001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.89259606599807995</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.90361022949219005</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.83080053329467995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.80003082752228005</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.78789383172989003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.78710055351257002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.78690278530121005</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.78032851219177002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.76915705204009999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.76983034610748002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.76991474628447998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.76210451126098999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.76324504613875999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.75206923484802002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.76296037435532005</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.75216430425643999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.75532370805740001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.74256753921509</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.73892277479171997</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.73824298381804998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.74144601821899003</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.73381584882735995</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.72748094797134</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.72514432668686002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72582536935805997</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.71874892711639005</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.72013884782791004</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.71924841403961004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.71712577342987005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.71662992238998002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.72472494840622004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.70936220884322998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.69820392131804998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.68987339735030995</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.68802946805954002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.69250911474228005</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.69081181287766003</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.69147115945815996</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.68581539392471003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.68021816015243997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68375444412231001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.68681472539902</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.68708336353302002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.68218737840652</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.69401586055756004</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.69173425436019997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.67598456144332997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.67763650417328003</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.67841529846190995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.67467319965363004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.68387293815613004</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.68034273386001998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.68033671379089</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.68260955810546997</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.67443764209747004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.67914330959320002</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.67708629369735995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.67256402969359996</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.67768996953964</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.67586934566498003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.67533004283904996</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.67051649093627996</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.67692214250564997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.68183654546738004</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.67157560586928999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.67005044221877996</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.67227947711945002</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.67463409900664995</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.66906577348708995</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.66290527582169001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.67526853084563998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.67312425374984997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.66384434700011996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.66846781969070002</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.67119771242142001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.66236078739166004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.66920840740204002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.66769844293594005</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.66950136423110995</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.66684406995773005</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.66741394996643</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.66634470224380005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.66678345203400002</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.66316658258437999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.66188192367554</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.66320151090622004</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.65727442502974998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.67609947919846003</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.66167116165161</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.66182345151901001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.66000795364380005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.66879117488860995</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.66523331403732</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.66352319717407005</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.66349363327026001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.66560417413712003</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.66024339199065996</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.65825492143631004</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.66037970781326005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.66175103187561002</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.66021662950516002</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.66000962257384999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.66417700052260997</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.65122139453887995</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.65798401832580999</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.65598350763321001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.65451425313949996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.66527813673018998</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.65370351076125999</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.65338259935378995</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.65456831455231002</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.65266078710555997</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.66042584180831998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.65117979049682995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.65773677825928001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.65804326534270996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.64781945943831998</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.65182799100875999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.65531468391418002</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.65116077661514005</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.65085798501967995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.64598214626312001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.65009653568268</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.65241485834122004</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.65296119451523005</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.64257222414017001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.65040284395217995</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.65050595998764005</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.65029805898666004</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.65243500471115001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.64848917722702004</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.65267115831375</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.64629203081131004</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.64366763830185003</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.64368426799774003</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.65140151977538996</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.64762634038925004</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.64197736978530995</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.64283907413482999</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.65015321969985995</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.63833272457123003</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.64979982376098999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.64361178874969005</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.64200788736342995</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.64274299144744995</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.64151966571807995</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.63740879297256003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.64138352870940996</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.64177381992339999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.64226359128952004</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.64727646112442005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.63579326868056996</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.64399790763855003</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.63754063844680997</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.63304144144058005</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.64059734344482</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.63862478733062999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.64382725954055997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.63444602489471003</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.63770157098769997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.63864731788634999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.63362580537795998</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.63648098707198997</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.64417660236358998</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.63457399606705001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.63827055692672996</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.63403081893920998</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.63915997743607</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.62996327877045</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.63424587249756004</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.63526856899260997</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.62732636928558005</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.62880814075470004</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.63018906116485995</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.62871754169464</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.63364851474761996</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.63177222013473999</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.63151830434798994</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.63606822490692005</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.62795424461365001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.62465864419937001</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.63500785827636996</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.63246124982833996</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.62248766422271995</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.62471240758895996</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.62781780958176003</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.63424676656723</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.62509107589722002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.62984251976012995</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.6232550740242</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.62869107723235995</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.625643491745</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.62965095043181996</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.62040036916732999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.62495261430740001</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.62477827072143999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.62174147367476995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.62538033723830999</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.62155485153197998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.61980527639389005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.62362462282180997</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.61650705337524003</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.61714786291122004</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.62161386013030995</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.62581014633179</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.61496883630752996</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.63054633140563998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.62374836206436002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.62215042114258001</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.62357413768768</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.62226361036301003</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.61762791872025002</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.61369776725768999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.61406075954437001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.62237358093261996</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.61404317617416004</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.61214011907578003</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.60362744331359997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.6160860657692</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.61678147315979004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.61115884780884</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.62058061361312999</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.61470067501068004</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.61079758405685003</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.62178897857666005</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.61141848564148005</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.60553473234177002</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.61033362150192005</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.60685878992080999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.61136513948440996</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.60736632347107</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.60223168134688998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.60869270563125999</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.61384242773055997</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.60882234573364002</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.61038088798523005</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.60640394687652999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.60980784893036</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.61263281106948997</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.60337948799133001</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.61346220970153997</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.60192245244980003</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.60510683059692005</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.60907703638077004</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.60989814996719005</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.60349583625793002</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.60650140047072998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.60594260692596003</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.61063706874847001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.60467219352722001</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.61172050237655995</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.59723961353302002</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.60951405763625999</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.60568690299988004</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.60417318344116</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.60714185237884999</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.60602873563766002</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.60009092092514005</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.59863734245300004</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.59709835052490001</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.59729039669036998</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.59869396686553999</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.60557097196579002</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.59698647260666005</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.60148632526398005</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.59903532266616999</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.59185552597045998</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.59384787082671997</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.59743016958237005</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.60152554512024003</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.59993463754653997</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.60144066810607999</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.59439849853516002</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.58889120817184004</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.59083771705626997</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.59273105859756003</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.59599107503891002</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.59030747413634999</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.58774048089981001</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.58280164003372004</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.59304714202881004</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.5954784154892</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.58754396438598999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.59086012840270996</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.59462344646454002</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.59390819072723</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.59825044870376998</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.59080630540848</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.59377431869507002</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.58437627553939997</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.59742039442062</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.58782732486724998</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.59141027927399004</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.58784109354018999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.58761453628539995</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.58488672971724998</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.58704209327697998</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.59094166755676003</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.58067506551742998</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.58555406332016002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.58505105972289995</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.58690524101257002</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.58450716733931996</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.58629256486893</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.57920229434966997</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.58189457654953003</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.58312696218491</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.58162289857864002</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.5861234664917</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.57904785871506004</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.58337271213530995</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.57686352729796997</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.57948267459868996</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.58045768737793002</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.58118981122971003</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.58691185712813998</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.58582657575607</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.58433008193970004</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.57133096456527999</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.57925266027450995</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.57413274049759</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.57557421922684004</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.57631897926330999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.58366733789444003</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.57956224679946999</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.57674151659011996</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.57845199108124001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.57828855514526001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.57975417375564997</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.57249563932419001</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.57214885950089001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.57411843538284002</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.57696282863616999</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.57227218151092996</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.58040148019791005</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.57468616962432995</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.58143436908722002</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.56927800178527999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.57960104942321999</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.57312339544295998</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.57618528604507002</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.57663750648499001</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.57285660505295</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.56652373075484996</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.57141607999802002</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.56885623931884999</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.56605666875839</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.57275027036667003</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.56716805696487005</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.56556379795073997</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.56860691308974998</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.56665545701981002</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.55756270885467996</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.56325238943099998</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.56794607639312999</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.56882566213607999</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.56647771596909002</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.56903928518294999</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.55689394474029996</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.56617408990859996</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.56762802600860995</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.56244212388991999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.56097650527954002</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.56447285413741999</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.55367952585220004</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.56133174896240001</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.56240791082382002</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.56094205379485995</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.56044572591782005</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.56646698713303001</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.55825304985045998</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.55903464555740001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.56410199403762995</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.56106901168822998</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.56194603443145996</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.56225794553757003</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.55817490816116</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.55940824747086004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.55307239294052002</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.55575817823410001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.55783081054688</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.55579960346222002</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.55684894323348999</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.56020772457123003</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.55834895372391002</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.55186831951141002</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.55347383022308005</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.55319404602051003</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.56091678142547996</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.55814170837402</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.55090177059173995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.54941534996033004</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.55794274806975996</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.55236214399338002</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.55097073316573997</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.55610853433608998</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.55156975984572998</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.55075782537460005</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.55138504505157004</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.54642039537429998</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.55230522155761996</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.54856395721436002</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.55178344249724998</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.54594129323958995</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.55098861455917003</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.54590451717376998</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.55110985040664995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.54773342609405995</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.55010902881622004</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.54891049861908003</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.55430179834366</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.54408347606659002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.54301697015761996</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.55048954486847002</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.54474425315857</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.54606527090072998</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.54355281591414994</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.54741942882537997</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.54531270265579002</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.53970211744308005</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.54389065504073997</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.54389286041259999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.54813659191132003</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.54029923677444003</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.54132914543152</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.54399508237839</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.54859685897827004</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.54602015018463002</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.54392653703689997</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.53627169132232999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.54210621118545999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.53788053989410001</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.53622096776962003</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.54354208707809004</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.53701698780060003</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.53618252277374001</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.53442192077636996</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.53679859638214</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.53910958766937001</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.53943747282027998</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.53262323141098</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.53464889526366999</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.54381310939788996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.53711748123169001</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.52948796749115001</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.54336220026016002</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.53102648258208995</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.53091269731521995</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.53247523307800004</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.53513622283936002</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.53836148977279996</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.52965354919434005</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.52863311767578003</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.53231972455978005</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.52467608451842995</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.52876657247543002</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.52638524770737005</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.53357666730881004</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.53293949365616</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.53173786401749001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.53014487028122004</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.53341072797775002</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.53427726030349998</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.53062808513641002</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.53003776073455999</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.53200578689574995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.52994835376740002</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.51979041099547996</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.53003072738646995</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.52739816904068004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.53156578540802002</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.52679747343062999</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C86-4175-A888-1C68D44C2A26}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$F$2:$F$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.4361934661864999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4307509660721001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4052577018737999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3754277229309</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3661518096923999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3501120805739999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3004044294357</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2764148712158001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2630277872086</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2126594781875999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1598023176193</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1371423006057999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1160435676575</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1636548042296999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.045276761055</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.99371296167374001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.0278086662292001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.98931795358658003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.94671553373337003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0286920070648</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.940185546875</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.98723405599594005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.88305371999741</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.91053789854050005</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.88849622011185003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.85853648185730003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.80953085422516002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.84911733865738004</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.81871610879898005</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.82156008481979004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.76237583160400002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.74671339988707996</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.77687740325928001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.74736100435257002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.74868392944336004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.72836571931839</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.73106151819229004</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.72806704044341997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.73575246334076005</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.72907245159149003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.72422081232071001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.71847593784331998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.71365159749984997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.71058726310730003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.70509552955626997</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.70530325174331998</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.70703458786010998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.70862483978270996</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.70495098829268998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.72236871719359996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.72097665071487005</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.68901306390761996</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.70739382505417003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.68891012668609997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.69268333911895996</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.68901318311690996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.67847937345505005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.68004256486893</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.67718452215195002</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.68661648035049005</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.66792684793472001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.66277772188187001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.66541266441345004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.66182440519332997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.66285985708237005</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.66303002834320002</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66351169347762995</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.66292148828506003</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.66474473476410001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.66265285015106001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.66209328174590998</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.66709977388382002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.66018623113632002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.66674137115479004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.66237974166869995</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.66118007898330999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.66257828474045</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.66542327404021995</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.66148191690445002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.66036611795425004</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.66117841005324995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.66140288114547996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.66057592630385997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.65853059291839999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.65999358892440996</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.66188651323318004</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.65792250633240001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.65890890359878995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.66175365447998002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.65896499156952004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.66266483068465998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.65893411636353005</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.65703976154327004</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.65795350074768</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.65979021787643</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.66289514303206998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.65925794839858998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.66066980361937999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.65910798311233998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.65752142667769997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.66536480188369995</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.66389930248259998</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.66129571199417003</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.66523420810698997</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.66035556793213002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.65967059135437001</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.65660750865936002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.65593016147614003</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.65442943572998002</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.65566879510880005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.65707021951675004</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.65316504240036</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.66011482477187999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.65230160951614002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.65362584590911998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.65058881044387995</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.65569585561751997</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.65105187892913996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.65730214118957997</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.65272849798203003</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.65191924571991</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.65411281585693004</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.65230619907378995</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.65147632360457997</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.64930856227875</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.65302526950836004</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.65301209688187001</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.65405458211899004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.65601843595505005</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.65109848976134999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.65261822938919001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.65386015176773005</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.65719109773635997</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.65102839469910001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.65074127912520996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.64682948589324996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.64929026365279996</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.65405982732773005</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.64795023202895996</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.64897894859313998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.65351706743240001</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.64676517248153997</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.65270948410034002</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.64852166175841996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.64923554658890004</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.64678204059600997</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.64842140674590998</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.64653384685516002</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.65552234649658003</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.65187388658524004</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.64557898044586004</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.64601957798003995</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.65502142906188998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.65161454677581998</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.64921116828918002</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.64012098312377996</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.64829117059707997</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.64436423778534002</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.65105843544006003</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.65071147680283004</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.64943343400955</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.64528810977936002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.64476436376571999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.64066499471663996</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.64791440963744995</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.64545118808746005</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.65082627534866</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.63826495409011996</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.63924223184586004</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.63564795255661</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.64335000514983998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.63993620872498003</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.64919883012771995</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.65243417024612005</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.64155817031859996</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.6458158493042</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.64306831359863004</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.63922154903411998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.65426355600357</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.64206492900848</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.64274334907532005</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.63450926542282005</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.64134812355042004</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.64199888706206998</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.63859307765961004</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.63307785987854004</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.64676868915557995</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.64108908176421997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.63432365655899003</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.64501684904098999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.63303607702255005</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.65184032917023005</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.64467781782150002</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.64287483692169001</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.63645887374877996</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.64468401670455999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.64038300514221003</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.63529145717621005</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.63284087181090998</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.64414280653</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.63833069801330999</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.63709586858749001</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.64945369958877996</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.63674116134643999</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.63963353633881004</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.63105607032776001</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.63966763019562001</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.63125163316726995</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.63474756479262995</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.63040822744369995</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.63240969181061002</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.63184380531311002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.63210546970366999</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.62853509187697998</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.63682943582535001</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.63018268346785999</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.62706339359283003</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.62762564420699996</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.63013684749603005</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.62570470571518</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.62745904922484996</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.63280564546585005</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.62563139200211004</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.63645488023758001</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.62563377618789995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.63472199440001997</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.63447284698485995</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.63061743974686002</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.63336658477783003</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.64411902427672996</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.63389110565186002</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.63759934902190996</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.63208329677581998</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.62914520502089999</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.63256752490997004</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.62937700748444003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.63697075843811002</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.62627696990966997</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.62222045660018999</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.62624162435532005</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.62974488735198997</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.63852208852768</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.62484544515609997</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.62388008832931996</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.62950974702835005</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.63307958841323997</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.62823170423508001</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.63096541166305997</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.62229984998703003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.62744200229644997</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.63735830783844005</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.62575042247771995</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.62191456556320002</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.62585502862929998</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.62310034036635997</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.62597191333770996</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.62109309434891002</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.62465822696686002</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.63010209798812999</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.62737405300140003</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.61740034818649003</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.62140136957169001</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.62461894750595004</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.61999863386153997</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.63139045238494995</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.61794149875641002</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.61867171525955</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.62353301048278997</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.62886297702788996</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.62240505218506004</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.61849862337112005</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.62328416109085005</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.61974108219146995</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.63293367624283003</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.61912447214126998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.61586773395537997</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.61618518829346003</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.61314970254898005</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.61647635698318004</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.62526214122771995</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.61402493715286</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.61564338207244995</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.61154192686080999</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.61596858501434004</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.61183881759643999</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.62156075239181996</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.60795140266418002</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.62896084785461004</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.61324298381804998</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.61766350269318004</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.61175030469893998</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.61600619554519997</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.61047440767287997</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.62007993459702004</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.62216216325759999</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.61615008115768</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.62262463569641002</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.62283438444137995</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.61182826757430997</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.61115849018097002</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.61128115653991999</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.61785548925400002</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.61346459388732999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.60389560461044001</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.62417799234390003</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.61264348030089999</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.6250776052475</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.62394541501999001</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.61457169055938998</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.60925060510634999</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.62205410003661998</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.61142462491989003</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.60166394710541005</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.63674569129944003</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.62179523706436002</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.61560881137848</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.60988730192184004</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.60760110616684004</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.60008782148360995</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.61690568923949995</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.60260307788848999</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.62595617771149004</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.60492575168609997</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.60891038179398005</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.60414391756057995</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.61476355791091997</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.61356246471404996</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.62517988681793002</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.60639345645904996</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.61394017934798994</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.63017266988753995</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.60859304666518999</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.60548090934752996</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.61299365758895996</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.60171061754226995</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.66663545370101995</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.67194026708603005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.61060231924056996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.60173338651657005</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.60817587375641002</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.60734343528748003</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.61804533004760998</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.59910911321640004</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.60789966583251998</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.60122996568679998</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.59656083583831998</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.60285353660582996</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.60145956277847001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.61086058616637995</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.61340099573134999</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.60503137111663996</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.60508275032043002</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.61127859354018999</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.61585837602615001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.61154156923294001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.59700286388396995</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.60763299465178999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.61689168214797996</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.59656029939651001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.60076278448105003</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.59530425071715998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.59724992513657005</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.59547591209411999</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.59990763664246005</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.59763425588607999</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.59245300292969005</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.59211146831511996</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.59349304437636996</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.59535980224608998</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.59873503446579002</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.60545182228088001</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.60026210546493997</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.59566736221312999</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.59291344881057995</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.60548651218413996</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.59448510408401001</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.59620797634125</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.61984151601791004</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.59519273042679</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.59804517030715998</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.61276441812515003</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.59673959016800004</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.59653663635253995</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.60913974046706998</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.59312725067139005</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.60541784763336004</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.59530615806580001</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.59171861410141002</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.60065883398055997</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.60030704736710006</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.59092539548874001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.60393702983856001</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.60319906473160001</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.61200153827667003</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.59669774770737005</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.60536849498749001</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.61706495285034002</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.60610175132750999</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.61129295825957997</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.59024178981780995</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.60544973611831998</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.59924131631850996</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.60055267810821999</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.60400575399399004</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.58661222457885998</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.58562302589417004</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.60190588235855003</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.59041762351990001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.58837240934372004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.60231596231461004</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.59107589721679998</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.59808027744293002</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.59140795469284002</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.59379458427428999</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.59425866603850996</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.60856026411056996</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.58861809968947998</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.60130608081818004</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.58786147832869995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.59691649675368996</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.58554255962372004</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.58953946828841997</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.59474676847457997</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.59888994693756004</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.58665198087692005</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.59278243780135997</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.59572386741637995</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.58991336822509999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.59166508913039995</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.59931957721710005</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.58525979518890003</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.59553438425063998</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.59644615650177002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.59883373975753995</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.59007048606873003</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.60907024145125999</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.59952729940413996</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.63677644729614002</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.60458850860596003</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.58986705541610995</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.59956026077270996</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.59056586027144997</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.60114771127701006</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.59629631042480002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.59349018335341996</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.58242964744568004</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.58812671899795999</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.59490752220153997</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.59070926904678001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.59605365991591996</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.58426707983017001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.58659875392913996</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.61475092172623003</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.60190719366073997</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.58706218004226995</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.58108228445053001</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.60289865732193004</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.59364825487136996</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.60121876001357999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.57755494117737005</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.59022361040115001</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.58361071348189997</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.61394006013869995</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.58312940597534002</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.59261262416839999</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.58893561363220004</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.59511393308640004</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.59788817167282005</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.59076535701751998</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.59031736850739003</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.58729511499404996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.60406601428985995</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.59386682510375999</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.58174538612366</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.59273743629455999</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.59412395954132002</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.59550172090529996</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.58716380596161</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.58415824174881004</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.58705812692642001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.58457297086715998</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.60028058290482</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.58216553926467995</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.57830303907393998</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.58640056848526001</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.58561581373214999</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.58254170417786</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.59765160083770996</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.59431689977645996</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.57976353168488004</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.58144265413284002</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.58583104610443004</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.59382694959641003</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.58641046285628995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.58390516042708995</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.58429884910582996</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.57986408472061002</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.59671485424042003</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.57700878381729004</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.58154201507568004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5C86-4175-A888-1C68D44C2A26}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="603335664"/>
+        <c:axId val="609308064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="603335664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="609308064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="609308064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Loss</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="603335664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13781,6 +20764,86 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -16400,6 +23463,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -16590,6 +24685,606 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>186142</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Gráfico 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C3F1F31-0B34-4DC9-8EB6-0E357CA60798}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>608360</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Gráfico 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8E26F4F-161F-45C8-B3E4-6EC5CBCADADC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>369403</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>178904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>371059</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>72886</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Retângulo: Cantos Arredondados 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF8FD555-4853-4A2D-8E74-372EE99680CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17829142" y="14656904"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Loss</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>91110</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>157369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>122583</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>106015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Retângulo: Cantos Arredondados 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FD48C6F-8985-4544-9153-8FC5D1A20DB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16937936" y="16921369"/>
+          <a:ext cx="1257299" cy="710646"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Loss </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>41414</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>99391</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>429040</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>64603</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Conector de Seta Reta 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99626D9A-47FB-4076-9E19-45A82C63241B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8307457" y="14386891"/>
+          <a:ext cx="387626" cy="536712"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>109331</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>117609</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Conector de Seta Reta 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B9C4AD8-A095-4581-8811-94DEB3E466A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12052853" y="14014174"/>
+          <a:ext cx="578126" cy="771935"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>82826</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>182217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>49696</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Conector de Seta Reta 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC946A6B-92F4-4876-9F38-2E979C945A69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18155478" y="16374717"/>
+          <a:ext cx="579783" cy="579783"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>505239</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>56322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>405848</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Conector de Seta Reta 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CA938BB-4A2C-4854-B101-A07AD191C6B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="17352065" y="15296322"/>
+          <a:ext cx="513522" cy="540026"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>140804</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>91109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142460</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>175591</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Retângulo: Cantos Arredondados 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3533C23B-BB43-454B-8E93-5A59075ECBBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10858500" y="14759609"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>367747</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>28160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>369403</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>112642</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Retângulo: Cantos Arredondados 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9D17740-AB4A-432A-ADC9-B96F1A646819}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8633790" y="14887160"/>
+          <a:ext cx="1227483" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
